--- a/排阵/对阵表.xlsx
+++ b/排阵/对阵表.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -540,19 +540,19 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/高洁</t>
+          <t>林锋/崔倩男</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>崔倩男/唐英武</t>
+          <t>罗琴荩/林小连</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/江锐</t>
+          <t>严勇文/王小波</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>王小波/程建兴</t>
+          <t>卢志辉/程建兴</t>
         </is>
       </c>
     </row>
@@ -599,14 +599,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/张欣欣</t>
+          <t>罗蒙/张欣欣</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/林锋</t>
+          <t>陈顺星/江锐</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>崔倩男/林小连</t>
+          <t>陈顺星/崔倩男</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/谢卓珊</t>
+          <t>罗琴荩/唐英武</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,19 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/唐英武</t>
+          <t>林锋/张欣欣</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/高洁</t>
+          <t>严勇文/卢志辉</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/林锋</t>
+          <t>罗蒙/江锐</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>王小波/程建兴</t>
         </is>
       </c>
     </row>
@@ -702,19 +702,19 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>崔倩男/林小连</t>
+          <t>陈顺星/崔倩男</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>谢卓珊/高洁</t>
+          <t>罗琴荩/林小连</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>王小波/李祺祺</t>
+          <t>卢志辉/江锐</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/唐英武</t>
+          <t>严勇文/程建兴</t>
         </is>
       </c>
     </row>
@@ -761,14 +761,14 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/陈小洪</t>
+          <t>王小波/林锋</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>严勇文/程建兴</t>
+          <t>罗蒙/张欣欣</t>
         </is>
       </c>
     </row>
@@ -783,19 +783,19 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>崔倩男/谢卓珊</t>
+          <t>王小波/崔倩男</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>高洁/林小连</t>
+          <t>陈顺星/唐英武</t>
         </is>
       </c>
     </row>
@@ -810,19 +810,19 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>王小波/李祺祺</t>
+          <t>卢志辉/江锐</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>林锋/唐英武</t>
+          <t>张欣欣/程建兴</t>
         </is>
       </c>
     </row>
@@ -837,19 +837,19 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>男双 (乱打)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>江锐/张欣欣</t>
+          <t>罗蒙/罗琴荩</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/卢志辉</t>
+          <t>林锋/林小连</t>
         </is>
       </c>
     </row>
@@ -864,19 +864,19 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/谢卓珊</t>
+          <t>林锋/唐英武</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>高洁/林小连</t>
+          <t>罗琴荩/林小连</t>
         </is>
       </c>
     </row>
@@ -896,41 +896,41 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/卢志辉</t>
+          <t>罗蒙/江锐</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/罗琴荩</t>
+          <t>卢志辉/张欣欣</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3号</t>
+          <t>1号</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/张欣欣</t>
+          <t>王小波/唐英武</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>江锐/程建兴</t>
+          <t>陈顺星/林小连</t>
         </is>
       </c>
     </row>
@@ -940,78 +940,24 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>2号</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>谢卓珊/林小连</t>
+          <t>罗蒙/罗琴荩</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/唐英武</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2号</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>男双</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>林锋/程建兴</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>陈顺星/江锐</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>3号</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>男双</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>罗蒙/卢志辉</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>王小波/罗琴荩</t>
+          <t>张欣欣/程建兴</t>
         </is>
       </c>
     </row>
@@ -1031,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1101,10 +1047,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -1120,10 +1066,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -1139,7 +1085,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>3</v>
@@ -1148,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1158,10 +1104,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
@@ -1177,10 +1123,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>0</v>
@@ -1196,10 +1142,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -1215,7 +1161,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>2</v>
@@ -1224,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1234,10 +1180,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
@@ -1249,153 +1195,77 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>陈小洪</t>
+          <t>陈顺星</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>陈顺星</t>
+          <t>唐英武</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
         <v>4</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>唐英武</t>
+          <t>崔倩男</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>崔倩男</t>
+          <t>林小连</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>李祺祺</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>林小连</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>谢卓珊</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>高洁</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/排阵/对阵表.xlsx
+++ b/排阵/对阵表.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -540,19 +540,19 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>林锋/崔倩男</t>
+          <t>唐英武/崔倩男</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/林小连</t>
+          <t>李祺祺/田茜</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/王小波</t>
+          <t>王小波/苏大哲</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>卢志辉/程建兴</t>
+          <t>刘继宇/严勇文</t>
         </is>
       </c>
     </row>
@@ -599,14 +599,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/张欣欣</t>
+          <t>陈顺星/陈小洪</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/江锐</t>
+          <t>罗蒙/林锋</t>
         </is>
       </c>
     </row>
@@ -626,14 +626,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/崔倩男</t>
+          <t>王小波/滕菲</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/唐英武</t>
+          <t>罗琴荩/崔倩男</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,19 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>林锋/张欣欣</t>
+          <t>林锋/唐英武</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>陈顺星/田茜</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/江锐</t>
+          <t>卢志辉/严勇文</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>王小波/程建兴</t>
+          <t>江锐/黄冬青</t>
         </is>
       </c>
     </row>
@@ -702,19 +702,19 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/崔倩男</t>
+          <t>滕菲/唐英武</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/林小连</t>
+          <t>李祺祺/崔倩男</t>
         </is>
       </c>
     </row>
@@ -734,14 +734,14 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>卢志辉/江锐</t>
+          <t>张欣欣/卢志辉</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>严勇文/程建兴</t>
+          <t>严勇文/陈小洪</t>
         </is>
       </c>
     </row>
@@ -761,14 +761,14 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>王小波/林锋</t>
+          <t>罗蒙/江锐</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/张欣欣</t>
+          <t>刘继宇/苏大哲</t>
         </is>
       </c>
     </row>
@@ -783,19 +783,19 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
+          <t>崔倩男/田茜</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/唐英武</t>
+          <t>滕菲/李祺祺</t>
         </is>
       </c>
     </row>
@@ -815,14 +815,14 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>卢志辉/江锐</t>
+          <t>黄冬青/严勇文</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>张欣欣/程建兴</t>
+          <t>张欣欣/罗琴荩</t>
         </is>
       </c>
     </row>
@@ -837,19 +837,19 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>男双 (乱打)</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/罗琴荩</t>
+          <t>王小波/陈顺星</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>林锋/林小连</t>
+          <t>刘继宇/林锋</t>
         </is>
       </c>
     </row>
@@ -869,14 +869,14 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>林锋/唐英武</t>
+          <t>罗琴荩/唐英武</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/林小连</t>
+          <t>陈顺星/崔倩男</t>
         </is>
       </c>
     </row>
@@ -891,46 +891,46 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/江锐</t>
+          <t>王小波/滕菲</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>卢志辉/张欣欣</t>
+          <t>林锋/田茜</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>3号</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>王小波/唐英武</t>
+          <t>罗蒙/严勇文</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/林小连</t>
+          <t>江锐/苏大哲</t>
         </is>
       </c>
     </row>
@@ -940,24 +940,240 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>1号</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/罗琴荩</t>
+          <t>滕菲/田茜</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>张欣欣/程建兴</t>
+          <t>李祺祺/唐英武</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2号</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>张欣欣/黄冬青</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>卢志辉/陈小洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>3号</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>罗琴荩/苏大哲</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>刘继宇/江锐</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1号</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>女双</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>李祺祺/田茜</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>滕菲/唐英武</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2号</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>罗蒙/陈小洪</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>张欣欣/卢志辉</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>3号</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>林锋/黄冬青</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>罗琴荩/苏大哲</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1号</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>陈顺星/陈小洪</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>刘继宇/王小波</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2号</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>江锐/黄冬青</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>罗蒙/卢志辉</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>3号</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>林锋/罗琴荩</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>张欣欣/苏大哲</t>
         </is>
       </c>
     </row>
@@ -977,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1028,10 +1244,10 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>0</v>
@@ -1043,7 +1259,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>卢志辉</t>
+          <t>刘继宇</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
@@ -1062,14 +1278,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>张欣欣</t>
+          <t>卢志辉</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -1081,77 +1297,77 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>林锋</t>
+          <t>张欣欣</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>江锐</t>
+          <t>林锋</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>王小波</t>
+          <t>江锐</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>程建兴</t>
+          <t>王小波</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1164,13 +1380,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1180,10 +1396,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>0</v>
@@ -1195,77 +1411,172 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>陈顺星</t>
+          <t>苏大哲</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>唐英武</t>
+          <t>陈小洪</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>崔倩男</t>
+          <t>陈顺星</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>林小连</t>
+          <t>黄冬青</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>唐英武</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="n">
         <v>4</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>崔倩男</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>李祺祺</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>滕菲</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>田茜</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/排阵/对阵表.xlsx
+++ b/排阵/对阵表.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -545,14 +545,14 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/崔倩男</t>
+          <t>滕菲/崔倩男</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>滕菲/田茜</t>
+          <t>李祺祺/田茜</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/陈顺星</t>
+          <t>罗蒙/陈小洪</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/王小波</t>
+          <t>严勇文/卢志辉</t>
         </is>
       </c>
     </row>
@@ -599,14 +599,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/林锋</t>
+          <t>林锋/罗琴荩</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈小洪</t>
+          <t>苏大哲/王小波</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>陈顺星/滕菲</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/黄冬青</t>
+          <t>罗琴荩/崔倩男</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,19 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/滕菲</t>
+          <t>黄冬青/陈小洪</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/崔倩男</t>
+          <t>严勇文/刘继宇</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
+          <t>王小波/田茜</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
+          <t>陈顺星/崔倩男</t>
         </is>
       </c>
     </row>
@@ -734,14 +734,14 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>严勇文/苏大哲</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈小洪</t>
+          <t>刘继宇/卢志辉</t>
         </is>
       </c>
     </row>
@@ -761,14 +761,14 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>林锋/滕菲</t>
+          <t>罗琴荩/滕菲</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
+          <t>王小波/田茜</t>
         </is>
       </c>
     </row>
@@ -788,14 +788,14 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>罗蒙/崔倩男</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
+          <t>林锋/田茜</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>严勇文/苏大哲</t>
+          <t>严勇文/刘继宇</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -842,14 +842,14 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/滕菲</t>
+          <t>陈顺星/李祺祺</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>林锋/田茜</t>
+          <t>罗琴荩/滕菲</t>
         </is>
       </c>
     </row>
@@ -869,14 +869,14 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/崔倩男</t>
+          <t>罗蒙/滕菲</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
+          <t>王小波/崔倩男</t>
         </is>
       </c>
     </row>
@@ -896,14 +896,14 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/卢志辉</t>
+          <t>严勇文/卢志辉</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>严勇文/苏大哲</t>
+          <t>苏大哲/黄冬青</t>
         </is>
       </c>
     </row>
@@ -923,14 +923,14 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/李祺祺</t>
+          <t>陈顺星/李祺祺</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>王小波/滕菲</t>
+          <t>林锋/田茜</t>
         </is>
       </c>
     </row>
@@ -950,14 +950,14 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>林锋/滕菲</t>
+          <t>林锋/李祺祺</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
+          <t>罗琴荩/滕菲</t>
         </is>
       </c>
     </row>
@@ -977,14 +977,14 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/卢志辉</t>
+          <t>苏大哲/陈小洪</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/陈小洪</t>
+          <t>刘继宇/卢志辉</t>
         </is>
       </c>
     </row>
@@ -1004,14 +1004,14 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/陈顺星</t>
+          <t>罗蒙/王小波</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/苏大哲</t>
+          <t>陈顺星/黄冬青</t>
         </is>
       </c>
     </row>
@@ -1031,14 +1031,14 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>林锋/李祺祺</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
+          <t>罗琴荩/田茜</t>
         </is>
       </c>
     </row>
@@ -1058,14 +1058,14 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/卢志辉</t>
+          <t>刘继宇/陈小洪</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/黄冬青</t>
+          <t>苏大哲/卢志辉</t>
         </is>
       </c>
     </row>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>林锋/苏大哲</t>
+          <t>罗蒙/黄冬青</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/罗琴荩</t>
+          <t>陈顺星/王小波</t>
         </is>
       </c>
     </row>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>陈顺星/滕菲</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/滕菲</t>
+          <t>王小波/田茜</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1139,41 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/卢志辉</t>
+          <t>苏大哲/刘继宇</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/黄冬青</t>
+          <t>陈小洪/卢志辉</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>3号</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>罗蒙/林锋</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>罗琴荩/黄冬青</t>
         </is>
       </c>
     </row>
@@ -1236,10 +1263,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -1274,7 +1301,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2</v>
@@ -1283,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1293,16 +1320,16 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1315,13 +1342,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1334,13 +1361,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1407,10 +1434,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>

--- a/排阵/对阵表.xlsx
+++ b/排阵/对阵表.xlsx
@@ -545,14 +545,14 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>滕菲/崔倩男</t>
+          <t>李祺祺/滕菲</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/田茜</t>
+          <t>崔倩男/田茜</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/陈小洪</t>
+          <t>严勇文/罗蒙</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>苏大哲/卢志辉</t>
         </is>
       </c>
     </row>
@@ -599,14 +599,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>林锋/罗琴荩</t>
+          <t>林锋/刘继宇</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/王小波</t>
+          <t>陈顺星/王小波</t>
         </is>
       </c>
     </row>
@@ -621,19 +621,19 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/滕菲</t>
+          <t>滕菲/崔倩男</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/崔倩男</t>
+          <t>李祺祺/田茜</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/陈小洪</t>
+          <t>罗琴荩/黄冬青</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>严勇文/刘继宇</t>
+          <t>严勇文/陈小洪</t>
         </is>
       </c>
     </row>
@@ -675,19 +675,19 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>林锋/李祺祺</t>
+          <t>罗蒙/苏大哲</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
+          <t>陈顺星/林锋</t>
         </is>
       </c>
     </row>
@@ -702,19 +702,19 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/李祺祺</t>
+          <t>崔倩男/田茜</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/崔倩男</t>
+          <t>李祺祺/滕菲</t>
         </is>
       </c>
     </row>
@@ -734,14 +734,14 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>严勇文/苏大哲</t>
+          <t>严勇文/卢志辉</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/卢志辉</t>
+          <t>刘继宇/王小波</t>
         </is>
       </c>
     </row>
@@ -756,19 +756,19 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/滕菲</t>
+          <t>林锋/罗琴荩</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
+          <t>黄冬青/陈小洪</t>
         </is>
       </c>
     </row>
@@ -783,19 +783,19 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/崔倩男</t>
+          <t>李祺祺/田茜</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>林锋/田茜</t>
+          <t>滕菲/崔倩男</t>
         </is>
       </c>
     </row>
@@ -815,14 +815,14 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>严勇文/刘继宇</t>
+          <t>罗琴荩/刘继宇</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/陈小洪</t>
+          <t>严勇文/王小波</t>
         </is>
       </c>
     </row>
@@ -837,19 +837,19 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>苏大哲/陈小洪</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/滕菲</t>
+          <t>陈顺星/卢志辉</t>
         </is>
       </c>
     </row>
@@ -864,19 +864,19 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/滕菲</t>
+          <t>李祺祺/崔倩男</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
+          <t>滕菲/田茜</t>
         </is>
       </c>
     </row>
@@ -896,14 +896,14 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>严勇文/黄冬青</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/黄冬青</t>
+          <t>罗蒙/卢志辉</t>
         </is>
       </c>
     </row>
@@ -918,19 +918,19 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>陈顺星/王小波</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>林锋/田茜</t>
+          <t>苏大哲/刘继宇</t>
         </is>
       </c>
     </row>
@@ -950,14 +950,14 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>林锋/李祺祺</t>
+          <t>林锋/滕菲</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/滕菲</t>
+          <t>罗琴荩/田茜</t>
         </is>
       </c>
     </row>
@@ -977,14 +977,14 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/陈小洪</t>
+          <t>罗蒙/陈顺星</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/卢志辉</t>
+          <t>黄冬青/陈小洪</t>
         </is>
       </c>
     </row>
@@ -1004,14 +1004,14 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/王小波</t>
+          <t>刘继宇/王小波</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/黄冬青</t>
+          <t>苏大哲/卢志辉</t>
         </is>
       </c>
     </row>
@@ -1031,14 +1031,14 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>林锋/李祺祺</t>
+          <t>罗蒙/李祺祺</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
+          <t>罗琴荩/滕菲</t>
         </is>
       </c>
     </row>
@@ -1058,14 +1058,14 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈小洪</t>
+          <t>黄冬青/王小波</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/卢志辉</t>
+          <t>林锋/陈小洪</t>
         </is>
       </c>
     </row>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/黄冬青</t>
+          <t>苏大哲/卢志辉</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/王小波</t>
+          <t>陈顺星/刘继宇</t>
         </is>
       </c>
     </row>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/滕菲</t>
+          <t>罗蒙/李祺祺</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
+          <t>林锋/田茜</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1139,14 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/刘继宇</t>
+          <t>刘继宇/陈小洪</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/卢志辉</t>
+          <t>罗琴荩/黄冬青</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/林锋</t>
+          <t>陈顺星/苏大哲</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/黄冬青</t>
+          <t>王小波/卢志辉</t>
         </is>
       </c>
     </row>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -1301,16 +1301,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1323,13 +1323,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>4</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>0</v>
@@ -1418,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1478,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/排阵/对阵表.xlsx
+++ b/排阵/对阵表.xlsx
@@ -545,14 +545,14 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/滕菲</t>
+          <t>李祺祺/田茜</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>崔倩男/田茜</t>
+          <t>滕菲/崔倩男</t>
         </is>
       </c>
     </row>
@@ -572,14 +572,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/罗蒙</t>
+          <t>严勇文/卢志辉</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/卢志辉</t>
+          <t>罗蒙/陈顺星</t>
         </is>
       </c>
     </row>
@@ -599,14 +599,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>林锋/刘继宇</t>
+          <t>林锋/罗琴荩</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/王小波</t>
+          <t>苏大哲/刘继宇</t>
         </is>
       </c>
     </row>
@@ -626,14 +626,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>滕菲/崔倩男</t>
+          <t>李祺祺/崔倩男</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/田茜</t>
+          <t>滕菲/田茜</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/黄冬青</t>
+          <t>严勇文/黄冬青</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>严勇文/陈小洪</t>
+          <t>陈小洪/王小波</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/苏大哲</t>
+          <t>林锋/罗琴荩</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/林锋</t>
+          <t>陈顺星/苏大哲</t>
         </is>
       </c>
     </row>
@@ -761,14 +761,14 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>林锋/罗琴荩</t>
+          <t>罗蒙/黄冬青</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/陈小洪</t>
+          <t>陈顺星/陈小洪</t>
         </is>
       </c>
     </row>
@@ -788,14 +788,14 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/田茜</t>
+          <t>滕菲/田茜</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>滕菲/崔倩男</t>
+          <t>李祺祺/崔倩男</t>
         </is>
       </c>
     </row>
@@ -815,14 +815,14 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/刘继宇</t>
+          <t>严勇文/罗蒙</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>严勇文/王小波</t>
+          <t>苏大哲/刘继宇</t>
         </is>
       </c>
     </row>
@@ -842,14 +842,14 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/陈小洪</t>
+          <t>林锋/罗琴荩</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/卢志辉</t>
+          <t>陈小洪/王小波</t>
         </is>
       </c>
     </row>
@@ -864,19 +864,19 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>女双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/崔倩男</t>
+          <t>陈顺星/李祺祺</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>滕菲/田茜</t>
+          <t>王小波/崔倩男</t>
         </is>
       </c>
     </row>
@@ -891,19 +891,19 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>严勇文/黄冬青</t>
+          <t>林锋/滕菲</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/卢志辉</t>
+          <t>罗琴荩/田茜</t>
         </is>
       </c>
     </row>
@@ -923,14 +923,14 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/王小波</t>
+          <t>严勇文/黄冬青</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/刘继宇</t>
+          <t>罗蒙/卢志辉</t>
         </is>
       </c>
     </row>
@@ -950,14 +950,14 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>林锋/滕菲</t>
+          <t>罗蒙/李祺祺</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
+          <t>陈顺星/田茜</t>
         </is>
       </c>
     </row>
@@ -977,14 +977,14 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/陈顺星</t>
+          <t>苏大哲/陈小洪</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/陈小洪</t>
+          <t>刘继宇/卢志辉</t>
         </is>
       </c>
     </row>
@@ -1004,14 +1004,14 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/王小波</t>
+          <t>罗琴荩/黄冬青</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/卢志辉</t>
+          <t>林锋/王小波</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/滕菲</t>
+          <t>林锋/滕菲</t>
         </is>
       </c>
     </row>
@@ -1058,14 +1058,14 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/王小波</t>
+          <t>苏大哲/刘继宇</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>林锋/陈小洪</t>
+          <t>陈小洪/卢志辉</t>
         </is>
       </c>
     </row>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/卢志辉</t>
+          <t>黄冬青/王小波</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/刘继宇</t>
+          <t>陈顺星/罗琴荩</t>
         </is>
       </c>
     </row>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/李祺祺</t>
+          <t>陈顺星/滕菲</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>林锋/田茜</t>
+          <t>王小波/田茜</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1139,14 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈小洪</t>
+          <t>刘继宇/卢志辉</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/黄冬青</t>
+          <t>苏大哲/陈小洪</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/苏大哲</t>
+          <t>罗蒙/罗琴荩</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>王小波/卢志辉</t>
+          <t>林锋/黄冬青</t>
         </is>
       </c>
     </row>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="D8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>0</v>
@@ -1418,13 +1418,13 @@
         <v>7</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1478,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
